--- a/output/pdf_financials_xlsx/NXE.xlsx
+++ b/output/pdf_financials_xlsx/NXE.xlsx
@@ -1222,19 +1222,19 @@
         <v>-8.3733</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4.647317</v>
+        <v>-4.647317</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>17.607441</v>
+        <v>-17.455889</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>56.797298</v>
+        <v>-56.863922</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-1.800904</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>17.480339</v>
+        <v>-15.615773</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1478,19 +1478,19 @@
         <v>-8.3733</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.647317</v>
+        <v>-4.647317</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>17.531665</v>
+        <v>-17.531665</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-1.491606</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>16.548056</v>
+        <v>-16.548056</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -1646,19 +1646,19 @@
         <v>-8.3733</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.647317</v>
+        <v>-4.647317</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>17.531665</v>
+        <v>-17.531665</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-1.491606</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>16.548056</v>
+        <v>-16.548056</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-126.948</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>232.36585</v>
+        <v>-232.36585</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>292.194417</v>
+        <v>-292.194417</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>334.297706</v>
+        <v>-334.297706</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1880,19 +1880,19 @@
         <v>-8.248542</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.840661</v>
+        <v>-4.453973</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>18.073946</v>
+        <v>-16.989384</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>58.103082</v>
+        <v>-55.558138</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.685661</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.295929</v>
+        <v>-13.800183</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1992,19 +1992,19 @@
         <v>-8.11354</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.086791</v>
+        <v>-4.207843</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>18.70091</v>
+        <v>-16.36242</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>58.861145</v>
+        <v>-54.800075</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>2.219295</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>21.679106</v>
+        <v>-11.417006</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2120,19 +2120,19 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.4303635037027811</v>
+        <v>-0.43409991894426</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.05865067736144772</v>
+        <v>-0.05858195992882798</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-17.17459675807261</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>5.333323341154882</v>
+        <v>-5.970136732904609</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -4966,43 +4966,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.187811</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.959329</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.53018</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>17.005665</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>28.050059</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>41.629049</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>51.559201</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>68.837</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>142.619</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>172.754</v>
       </c>
     </row>
     <row r="93">
@@ -5267,7 +5267,7 @@
         <v>-56.83061</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>1.491606</v>
+        <v>-1.491606</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-16.548056</v>
@@ -6138,13 +6138,13 @@
         <v>-40.183986</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.08774899999999999</v>
+        <v>-35.873093</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>34.813614</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.014354</v>
+        <v>-57.03594</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>-45.733</v>
@@ -8916,7 +8916,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12911,7 +12915,11 @@
           <t>Reserves (Note 11) 142,619</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16711,7 +16719,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -19027,7 +19039,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -23022,7 +23038,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -24221,7 +24241,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
         <v>0.0334</v>
       </c>
@@ -34511,7 +34535,7 @@
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>1.491606</v>
+        <v>-1.491606</v>
       </c>
       <c r="L348" s="5" t="n">
         <v>-16.548056</v>
@@ -35695,7 +35719,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -36890,7 +36918,7 @@
         <v>-56.83061</v>
       </c>
       <c r="K379" s="5" t="n">
-        <v>1.491606</v>
+        <v>-1.491606</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -37251,7 +37279,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -44478,13 +44510,13 @@
         </is>
       </c>
       <c r="J474" s="5" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="K474" s="5" t="n">
         <v>-1.491606</v>
       </c>
       <c r="L474" s="5" t="n">
-        <v>16.548056</v>
+        <v>-16.548056</v>
       </c>
       <c r="M474" t="inlineStr">
         <is>
@@ -44806,7 +44838,7 @@
         <v>-2.092427</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>18.892957</v>
+        <v>-18.892957</v>
       </c>
       <c r="M478" t="inlineStr">
         <is>
@@ -45035,13 +45067,13 @@
         </is>
       </c>
       <c r="J481" s="5" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="K481" s="5" t="n">
         <v>-1.491606</v>
       </c>
       <c r="L481" s="5" t="n">
-        <v>16.548056</v>
+        <v>-16.548056</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
@@ -45270,13 +45302,13 @@
         </is>
       </c>
       <c r="J484" s="5" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="K484" s="5" t="n">
         <v>-2.092427</v>
       </c>
       <c r="L484" s="5" t="n">
-        <v>18.892957</v>
+        <v>-18.892957</v>
       </c>
       <c r="M484" t="inlineStr">
         <is>
@@ -46267,7 +46299,7 @@
         </is>
       </c>
       <c r="J497" s="5" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="K497" s="5" t="n">
         <v>-2.092427</v>
@@ -47042,10 +47074,10 @@
         </is>
       </c>
       <c r="I507" s="5" t="n">
-        <v>17.531665</v>
+        <v>-17.531665</v>
       </c>
       <c r="J507" s="5" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
@@ -47283,10 +47315,10 @@
         </is>
       </c>
       <c r="I510" s="5" t="n">
-        <v>17.531665</v>
+        <v>-17.531665</v>
       </c>
       <c r="J510" s="5" t="n">
-        <v>56.83061</v>
+        <v>-56.83061</v>
       </c>
       <c r="K510" t="inlineStr">
         <is>
@@ -47908,10 +47940,10 @@
         </is>
       </c>
       <c r="H518" s="5" t="n">
-        <v>4.647317</v>
+        <v>-4.647317</v>
       </c>
       <c r="I518" s="5" t="n">
-        <v>17.531665</v>
+        <v>-17.531665</v>
       </c>
       <c r="J518" t="inlineStr">
         <is>
@@ -48070,10 +48102,10 @@
         </is>
       </c>
       <c r="H520" s="5" t="n">
-        <v>4.647317</v>
+        <v>-4.647317</v>
       </c>
       <c r="I520" s="5" t="n">
-        <v>17.531665</v>
+        <v>-17.531665</v>
       </c>
       <c r="J520" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NXE.xlsx
+++ b/output/pdf_financials_xlsx/NXE.xlsx
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.729746</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.562633</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>13.840457</v>
@@ -2270,19 +2270,19 @@
         <v>52.117581</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>201.804</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>134.447</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>134.447</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>476.587</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>802.578</v>
       </c>
     </row>
     <row r="35">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.729746</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.562633</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>13.840457</v>
@@ -2362,19 +2362,19 @@
         <v>52.117581</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>9.315</v>
+        <v>211.119</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>5.775</v>
+        <v>140.222</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>5.775</v>
+        <v>140.222</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>476.587</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>321.084</v>
+        <v>1123.662</v>
       </c>
     </row>
     <row r="37">
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.884513</v>
+        <v>0.154767</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7.903051</v>
+        <v>0.340418</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.158447</v>
@@ -2914,19 +2914,19 @@
         <v>0.73431</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>202.832</v>
+        <v>1.028</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>136.612</v>
+        <v>2.165</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>136.612</v>
+        <v>2.165</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>491.457</v>
+        <v>14.87</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>824.3099999999999</v>
+        <v>21.732</v>
       </c>
     </row>
     <row r="49">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -24551,7 +24551,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E231" s="5" t="n">
@@ -44025,7 +44025,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -46033,7 +46033,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -47609,7 +47609,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">

--- a/output/pdf_financials_xlsx/NXE.xlsx
+++ b/output/pdf_financials_xlsx/NXE.xlsx
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.176045</v>
+        <v>0.492105</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.73593</v>
+        <v>1.553582</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.614397</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.045677</v>
+        <v>2.27612</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.720437</v>
+        <v>4.742394</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2.142547</v>
+        <v>6.135824</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.776011</v>
+        <v>8.673505</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>3.138791</v>
+        <v>8.763125</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
@@ -886,19 +886,19 @@
         <v>0.614397</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.045677</v>
+        <v>2.27612</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.720437</v>
+        <v>4.742394</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.142547</v>
+        <v>6.135824</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2.776011</v>
+        <v>8.673505</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>3.138791</v>
+        <v>8.763125</v>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         <v>56.863922</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-2.776011</v>
+        <v>-8.673505</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-3.138791</v>
+        <v>-8.763125</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -3952,19 +3952,19 @@
         <v>0</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.926</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="71">
@@ -3998,19 +3998,19 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.926</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="72">
@@ -4182,19 +4182,19 @@
         <v>0.786482</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>2.844</v>
+        <v>2.069</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>82.86499999999999</v>
+        <v>82.09</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>459.428</v>
+        <v>458.502</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>590.029</v>
+        <v>589.332</v>
       </c>
     </row>
     <row r="76">
@@ -4427,30 +4427,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J80" s="3" t="n">
+        <v>0.001530298169711368</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.001701737089304967</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.001701737089304967</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.000785384053650382</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.0003804360878288834</v>
       </c>
     </row>
     <row r="81">
@@ -5776,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.206986</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>-0.016</v>
@@ -5788,10 +5778,10 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="111">
@@ -5801,34 +5791,34 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004496</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.19935</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.806246</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.347104</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-2.883571</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-1.859729</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-2.954028</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.6291600000000001</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.354</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>-6.066</v>
@@ -6885,34 +6875,34 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004496</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.19935</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.806246</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.347104</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-2.883571</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-1.859729</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-2.954028</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.6291600000000001</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.354</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>-6.066</v>
@@ -6931,34 +6921,34 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.538509</v>
+        <v>-0.543005</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.89042</v>
+        <v>-3.08977</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.028919</v>
+        <v>-2.835165</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.697822</v>
+        <v>-3.044926</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-8.024952000000001</v>
+        <v>-10.908523</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-11.144497</v>
+        <v>-13.004226</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-8.452068000000001</v>
+        <v>-11.406096</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-12.805886</v>
+        <v>-13.435046</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-16.788</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-20.176</v>
+        <v>-20.53</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-58.682</v>
@@ -8284,7 +8274,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12358,7 +12352,11 @@
           <t>Lease liabilities (Note 10(c)) 926</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -16245,7 +16243,11 @@
           <t>Lease liabilities (Note 11(c))</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -18567,7 +18569,11 @@
           <t>Lease liabilities (Note 10)</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -26250,7 +26256,11 @@
           <t>Interest on lease liabilities and accretion expense</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -29436,7 +29446,11 @@
           <t>Deferred income tax recovery (Note 18)</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -31597,7 +31611,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -31996,7 +32014,11 @@
           <t>Acquisition of equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -34959,7 +34981,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -35192,7 +35218,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -35802,7 +35832,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -37044,7 +37078,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -37362,7 +37400,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -39041,7 +39083,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -40993,7 +41039,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E430" s="5" t="n">
         <v>-0.004496</v>
       </c>
@@ -43277,7 +43327,11 @@
           <t>Salaries, benefits and directors’ fees 11 $</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -44639,7 +44693,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -45664,7 +45722,11 @@
           <t>Salaries, benefits and directors’ fees 10 $</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -46108,7 +46170,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -49446,7 +49512,11 @@
           <t>Salaries, benefits and directors fees 9</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E537" t="inlineStr">
         <is>
           <t>-</t>
@@ -49525,7 +49595,11 @@
           <t>Salaries, benefits and directors fees 10</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E538" s="5" t="n">
         <v>0.31606</v>
       </c>
